--- a/03_Group_comparisons/Proteome/03_Set_Contrasts/training/c_data/set_contrasts.xlsx
+++ b/03_Group_comparisons/Proteome/03_Set_Contrasts/training/c_data/set_contrasts.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3877" uniqueCount="1527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3907" uniqueCount="1545">
   <si>
     <t>sheet</t>
   </si>
@@ -4139,7 +4139,7 @@
     <t>fit</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/03_Protein_Contrasts/training/c_data/fit.rds</t>
+    <t>03_Group_comparisons/Proteome/02_Protein_Contrasts/training/c_data/fit.rds</t>
   </si>
   <si>
     <t>aacf5e18d593ba8d0ecb1981394483bd</t>
@@ -4148,7 +4148,7 @@
     <t>design</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/02_Design_Contrasts/training/c_data/design.rds</t>
+    <t>03_Group_comparisons/Proteome/01_Design_Contrasts/training/c_data/design.rds</t>
   </si>
   <si>
     <t>614bbdf4f0c26542c91ed8556721be1c</t>
@@ -4172,7 +4172,7 @@
     <t>phenotype</t>
   </si>
   <si>
-    <t>00_Input/phenotype.csv</t>
+    <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
     <t>5a1989db406daa0b70189a9f0df52cf3</t>
@@ -4301,12 +4301,21 @@
     <t>Github (Dustyn-T-Lewis/enrichVolcano@d3fed631f4ae95e01bd61137699313f8de5cc86e)</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
     <t>fastmatch</t>
   </si>
   <si>
@@ -4367,6 +4376,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -4379,6 +4400,18 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -4394,9 +4427,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -4421,6 +4451,12 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
     <t>pillar</t>
   </si>
   <si>
@@ -4505,6 +4541,12 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -4580,6 +4622,12 @@
     <t>0.5.0</t>
   </si>
   <si>
+    <t>utf8</t>
+  </si>
+  <si>
+    <t>1.2.6</t>
+  </si>
+  <si>
     <t>vctrs</t>
   </si>
   <si>
@@ -4598,10 +4646,16 @@
     <t>3.0.2</t>
   </si>
   <si>
-    <t>writexl</t>
-  </si>
-  <si>
-    <t>2.0.1</t>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -26371,7 +26425,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -26618,13 +26672,13 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>1430</v>
       </c>
       <c r="B23" t="s">
-        <v>1430</v>
+        <v>1412</v>
       </c>
       <c r="C23" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -26640,21 +26694,21 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" t="s">
         <v>1433</v>
       </c>
-      <c r="B25" t="s">
-        <v>1434</v>
-      </c>
       <c r="C25" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B26" t="s">
         <v>1435</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1436</v>
       </c>
       <c r="C26" t="s">
         <v>1390</v>
@@ -26662,10 +26716,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B27" t="s">
         <v>1437</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1438</v>
       </c>
       <c r="C27" t="s">
         <v>1390</v>
@@ -26673,10 +26727,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B28" t="s">
         <v>1439</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1434</v>
       </c>
       <c r="C28" t="s">
         <v>1390</v>
@@ -26698,7 +26752,7 @@
         <v>1442</v>
       </c>
       <c r="B30" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="C30" t="s">
         <v>1390</v>
@@ -26706,10 +26760,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B31" t="s">
         <v>1444</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1445</v>
       </c>
       <c r="C31" t="s">
         <v>1390</v>
@@ -26717,10 +26771,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B32" t="s">
         <v>1446</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1447</v>
       </c>
       <c r="C32" t="s">
         <v>1390</v>
@@ -26728,21 +26782,21 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B33" t="s">
         <v>1448</v>
       </c>
-      <c r="B33" t="s">
-        <v>1449</v>
-      </c>
       <c r="C33" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B34" t="s">
         <v>1450</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1451</v>
       </c>
       <c r="C34" t="s">
         <v>1390</v>
@@ -26750,10 +26804,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B35" t="s">
         <v>1452</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1453</v>
       </c>
       <c r="C35" t="s">
         <v>1390</v>
@@ -26761,10 +26815,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B36" t="s">
         <v>1454</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1455</v>
       </c>
       <c r="C36" t="s">
         <v>1390</v>
@@ -26772,32 +26826,32 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B37" t="s">
         <v>1456</v>
       </c>
-      <c r="B37" t="s">
-        <v>1457</v>
-      </c>
       <c r="C37" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B38" t="s">
         <v>1458</v>
       </c>
-      <c r="B38" t="s">
-        <v>1459</v>
-      </c>
       <c r="C38" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B39" t="s">
         <v>1460</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1461</v>
       </c>
       <c r="C39" t="s">
         <v>1390</v>
@@ -26805,10 +26859,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B40" t="s">
         <v>1462</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1463</v>
       </c>
       <c r="C40" t="s">
         <v>1390</v>
@@ -26816,10 +26870,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B41" t="s">
         <v>1464</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1465</v>
       </c>
       <c r="C41" t="s">
         <v>1390</v>
@@ -26827,10 +26881,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B42" t="s">
         <v>1466</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1467</v>
       </c>
       <c r="C42" t="s">
         <v>1390</v>
@@ -26838,10 +26892,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B43" t="s">
-        <v>1469</v>
+        <v>1427</v>
       </c>
       <c r="C43" t="s">
         <v>1390</v>
@@ -26849,21 +26903,21 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="B44" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="C44" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="B45" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="C45" t="s">
         <v>1390</v>
@@ -26871,10 +26925,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="B46" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="C46" t="s">
         <v>1390</v>
@@ -26882,21 +26936,21 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>1474</v>
       </c>
       <c r="B47" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="C47" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B48" t="s">
         <v>1477</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1478</v>
       </c>
       <c r="C48" t="s">
         <v>1390</v>
@@ -26904,10 +26958,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B49" t="s">
         <v>1479</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1480</v>
       </c>
       <c r="C49" t="s">
         <v>1390</v>
@@ -26915,10 +26969,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B50" t="s">
         <v>1481</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1482</v>
       </c>
       <c r="C50" t="s">
         <v>1390</v>
@@ -26926,10 +26980,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B51" t="s">
         <v>1483</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1484</v>
       </c>
       <c r="C51" t="s">
         <v>1390</v>
@@ -26937,10 +26991,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B52" t="s">
         <v>1485</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1486</v>
       </c>
       <c r="C52" t="s">
         <v>1390</v>
@@ -26948,10 +27002,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B53" t="s">
         <v>1487</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1488</v>
       </c>
       <c r="C53" t="s">
         <v>1390</v>
@@ -26959,32 +27013,32 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>1489</v>
+        <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="C54" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B55" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="C55" t="s">
-        <v>1493</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="B56" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="C56" t="s">
         <v>1390</v>
@@ -26992,21 +27046,21 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="B57" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="C57" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="B58" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="C58" t="s">
         <v>1390</v>
@@ -27014,10 +27068,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="B59" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="C59" t="s">
         <v>1390</v>
@@ -27025,10 +27079,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="B60" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="C60" t="s">
         <v>1390</v>
@@ -27036,10 +27090,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="B61" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="C61" t="s">
         <v>1390</v>
@@ -27047,21 +27101,21 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="B62" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="C62" t="s">
-        <v>1390</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="B63" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="C63" t="s">
         <v>1390</v>
@@ -27069,10 +27123,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="B64" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="C64" t="s">
         <v>1390</v>
@@ -27080,21 +27134,21 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="B65" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="C65" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="B66" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="C66" t="s">
         <v>1390</v>
@@ -27102,10 +27156,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B67" t="s">
-        <v>1422</v>
+        <v>1515</v>
       </c>
       <c r="C67" t="s">
         <v>1390</v>
@@ -27113,10 +27167,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B68" t="s">
         <v>1517</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1518</v>
       </c>
       <c r="C68" t="s">
         <v>1390</v>
@@ -27124,10 +27178,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B69" t="s">
         <v>1519</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1520</v>
       </c>
       <c r="C69" t="s">
         <v>1390</v>
@@ -27135,10 +27189,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B70" t="s">
         <v>1521</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1522</v>
       </c>
       <c r="C70" t="s">
         <v>1390</v>
@@ -27146,10 +27200,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B71" t="s">
         <v>1523</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1524</v>
       </c>
       <c r="C71" t="s">
         <v>1390</v>
@@ -27157,13 +27211,123 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B72" t="s">
         <v>1525</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
         <v>1526</v>
       </c>
-      <c r="C72" t="s">
-        <v>1493</v>
+      <c r="B73" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1390</v>
       </c>
     </row>
   </sheetData>
